--- a/consent_forms/011_parent_guardian_attestation--consent_forms.xlsx
+++ b/consent_forms/011_parent_guardian_attestation--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -638,12 +638,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'fever'}</t>
+          <t>fever</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Fever'}</t>
+          <t>Fever</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'cough'}</t>
+          <t>cough</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Cough'}</t>
+          <t>Cough</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'shortness_of_breath'}</t>
+          <t>shortness_of_breath</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Shortness of Breath'}</t>
+          <t>Shortness of Breath</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'loss_of_smell'}</t>
+          <t>loss_of_smell</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Loss of Smell'}</t>
+          <t>Loss of Smell</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'sore_throat'}</t>
+          <t>sore_throat</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Sore Throat'}</t>
+          <t>Sore Throat</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'runny_nose'}</t>
+          <t>runny_nose</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Runny Nose'}</t>
+          <t>Runny Nose</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'headache'}</t>
+          <t>headache</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Headache'}</t>
+          <t>Headache</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'fatigue'}</t>
+          <t>fatigue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Fatigue'}</t>
+          <t>Fatigue</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'muscle_aches'}</t>
+          <t>muscle_aches</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Muscle Aches'}</t>
+          <t>Muscle Aches</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'nausea'}</t>
+          <t>nausea</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Nausea'}</t>
+          <t>Nausea</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'diarrhea'}</t>
+          <t>diarrhea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Diarrhea'}</t>
+          <t>Diarrhea</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'vomiting'}</t>
+          <t>vomiting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Vomiting'}</t>
+          <t>Vomiting</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'confusion'}</t>
+          <t>confusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Confusion'}</t>
+          <t>Confusion</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'loss_of_speech'}</t>
+          <t>loss_of_speech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Loss of Speech'}</t>
+          <t>Loss of Speech</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'loss_of_appetite'}</t>
+          <t>loss_of_appetite</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Loss of Appetite'}</t>
+          <t>Loss of Appetite</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'loss_of_taste'}</t>
+          <t>loss_of_taste</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Loss of Taste'}</t>
+          <t>Loss of Taste</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_describe)'}</t>
+          <t>other_(please_describe)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please describe)'}</t>
+          <t>Other (please describe)</t>
         </is>
       </c>
     </row>
@@ -960,63 +960,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'none_of_the_above'}</t>
+          <t>none_of_the_above</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'None of the above'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'label':_'none_of_the_above'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'label': 'None of the above'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'label':_'none_of_the_above'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'label': 'None of the above'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>covid_symptoms_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'label':_'none_of_the_above'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'label': 'None of the above'}</t>
+          <t>None of the above</t>
         </is>
       </c>
     </row>
